--- a/数据表/Datas/CharacterConfig_角色配置.xlsx
+++ b/数据表/Datas/CharacterConfig_角色配置.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Seek-Battle-Evacuate\数据表\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -99,7 +104,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -108,7 +113,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>ID</t>
@@ -119,7 +124,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>原型名</t>
@@ -130,7 +135,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>新存档拥有</t>
@@ -141,7 +146,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>基础</t>
@@ -150,7 +155,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>HP</t>
@@ -159,7 +164,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>上限</t>
@@ -170,7 +175,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>基础</t>
@@ -179,7 +184,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>MP</t>
@@ -188,7 +193,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>上限</t>
@@ -199,7 +204,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>攻击力</t>
@@ -210,7 +215,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>魔力</t>
@@ -221,7 +226,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>速度</t>
@@ -232,7 +237,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>普通攻击行动</t>
@@ -241,7 +246,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>ID</t>
@@ -252,7 +257,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>唯一技能行动</t>
@@ -261,7 +266,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>ID</t>
@@ -272,7 +277,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>初始武器</t>
@@ -281,7 +286,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>ID</t>
@@ -290,7 +295,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>，</t>
@@ -299,7 +304,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>0</t>
@@ -308,7 +313,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>为空</t>
@@ -319,7 +324,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>初始防具</t>
@@ -328,7 +333,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>ID</t>
@@ -337,7 +342,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>，</t>
@@ -346,7 +351,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>0</t>
@@ -355,7 +360,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>为空</t>
@@ -366,7 +371,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>图标资源配置</t>
@@ -377,7 +382,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -386,7 +391,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -397,7 +402,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -406,7 +411,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>2</t>
@@ -417,7 +422,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -426,7 +431,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>3</t>
@@ -437,7 +442,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -446,7 +451,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>4</t>
@@ -457,7 +462,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -466,7 +471,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>5</t>
@@ -477,7 +482,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -486,7 +491,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>6</t>
@@ -497,7 +502,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -506,7 +511,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>7</t>
@@ -517,7 +522,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -526,7 +531,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>8</t>
@@ -537,7 +542,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -546,7 +551,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>9</t>
@@ -557,7 +562,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -566,7 +571,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>10</t>
@@ -577,7 +582,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -586,7 +591,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>11</t>
@@ -597,7 +602,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -606,7 +611,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>12</t>
@@ -617,7 +622,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -626,7 +631,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>13</t>
@@ -637,7 +642,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -646,7 +651,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>14</t>
@@ -657,7 +662,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -666,7 +671,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>15</t>
@@ -691,43 +696,37 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF006100"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F4E78"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF595959"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -884,7 +883,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1280,153 +1285,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1462,9 +1467,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1939,7 +1941,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="3" width="10" style="2" customWidth="1"/>
@@ -1947,13 +1949,13 @@
     <col min="5" max="9" width="10" style="2" customWidth="1"/>
     <col min="10" max="10" width="17" style="2" customWidth="1"/>
     <col min="11" max="11" width="15" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.8676470588235" style="2" customWidth="1"/>
-    <col min="13" max="13" width="18.2573529411765" style="2" customWidth="1"/>
-    <col min="14" max="14" width="33.2058823529412" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.8666666666667" style="2" customWidth="1"/>
+    <col min="13" max="13" width="18.2583333333333" style="2" customWidth="1"/>
+    <col min="14" max="14" width="33.2083333333333" style="2" customWidth="1"/>
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:14">
+    <row r="1" customHeight="1" spans="1:14">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1997,7 +1999,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:14">
+    <row r="2" customHeight="1" spans="1:14">
       <c r="A2" s="5" t="s">
         <v>14</v>
       </c>
@@ -2041,7 +2043,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1" spans="1:14">
+    <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="7" t="s">
         <v>19</v>
       </c>
@@ -2083,7 +2085,7 @@
       </c>
       <c r="N3" s="8"/>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:14">
+    <row r="4" customHeight="1" spans="1:14">
       <c r="A4" s="9" t="s">
         <v>21</v>
       </c>
@@ -2127,12 +2129,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1" spans="1:14">
+    <row r="5" customHeight="1" spans="1:14">
       <c r="A5" s="11"/>
       <c r="B5" s="12">
         <v>1001</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="12" t="s">
         <v>35</v>
       </c>
       <c r="D5" s="12" t="b">
@@ -2165,11 +2167,11 @@
       <c r="M5" s="12">
         <v>0</v>
       </c>
-      <c r="N5" s="13" t="s">
+      <c r="N5" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1" spans="1:14">
+    <row r="6" customHeight="1" spans="1:14">
       <c r="A6" s="11"/>
       <c r="B6" s="12">
         <v>1002</v>
@@ -2211,7 +2213,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1" spans="1:14">
+    <row r="7" customHeight="1" spans="1:14">
       <c r="A7" s="11"/>
       <c r="B7" s="12">
         <v>1003</v>
@@ -2253,7 +2255,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1" spans="1:14">
+    <row r="8" customHeight="1" spans="1:14">
       <c r="A8" s="11"/>
       <c r="B8" s="12">
         <v>1004</v>
@@ -2295,11 +2297,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" ht="18" spans="1:14">
+    <row r="9" customHeight="1" spans="1:14">
       <c r="B9" s="12">
         <v>1005</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>39</v>
       </c>
       <c r="D9" s="2" t="b">
@@ -2332,11 +2334,11 @@
       <c r="M9" s="12">
         <v>0</v>
       </c>
-      <c r="N9" s="13" t="s">
+      <c r="N9" s="12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" ht="18" spans="1:14">
+    <row r="10" customHeight="1" spans="1:14">
       <c r="B10" s="12">
         <v>1006</v>
       </c>
@@ -2377,7 +2379,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" ht="18" spans="1:14">
+    <row r="11" customHeight="1" spans="1:14">
       <c r="B11" s="12">
         <v>1007</v>
       </c>
@@ -2418,7 +2420,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" ht="18" spans="1:14">
+    <row r="12" customHeight="1" spans="1:14">
       <c r="B12" s="12">
         <v>1008</v>
       </c>
@@ -2459,11 +2461,11 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" ht="18" spans="1:14">
+    <row r="13" customHeight="1" spans="1:14">
       <c r="B13" s="12">
         <v>1009</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>43</v>
       </c>
       <c r="D13" s="2" t="b">
@@ -2496,11 +2498,11 @@
       <c r="M13" s="12">
         <v>0</v>
       </c>
-      <c r="N13" s="13" t="s">
+      <c r="N13" s="12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" ht="18" spans="1:14">
+    <row r="14" customHeight="1" spans="1:14">
       <c r="B14" s="12">
         <v>1010</v>
       </c>
@@ -2541,7 +2543,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" ht="18" spans="1:14">
+    <row r="15" customHeight="1" spans="1:14">
       <c r="B15" s="12">
         <v>1011</v>
       </c>
@@ -2582,7 +2584,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" ht="18" spans="1:14">
+    <row r="16" customHeight="1" spans="1:14">
       <c r="B16" s="12">
         <v>1012</v>
       </c>
@@ -2623,11 +2625,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" ht="18" spans="2:14">
+    <row r="17" customHeight="1" spans="2:14">
       <c r="B17" s="12">
         <v>1013</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="12" t="s">
         <v>47</v>
       </c>
       <c r="D17" s="2" t="b">
@@ -2660,11 +2662,11 @@
       <c r="M17" s="12">
         <v>0</v>
       </c>
-      <c r="N17" s="13" t="s">
+      <c r="N17" s="12" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" ht="18" spans="2:14">
+    <row r="18" customHeight="1" spans="2:14">
       <c r="B18" s="12">
         <v>1014</v>
       </c>
@@ -2705,7 +2707,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" ht="18" spans="2:14">
+    <row r="19" customHeight="1" spans="2:14">
       <c r="B19" s="12">
         <v>1015</v>
       </c>
